--- a/data/trans_dic/P57B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P57B_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat)</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,68</t>
+          <t>0,46; 5,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 12,67</t>
+          <t>4,5; 12,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,96</t>
+          <t>2,59; 6,96</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 9,23</t>
+          <t>3,38; 8,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,51</t>
+          <t>3,65; 8,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,77</t>
+          <t>4,15; 8,01</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,53</t>
+          <t>5,84; 10,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 9,74</t>
+          <t>6,15; 9,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 9,56</t>
+          <t>6,56; 9,58</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 11,09</t>
+          <t>3,47; 11,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,22; 13,39</t>
+          <t>9,41; 13,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,55; 11,31</t>
+          <t>5,61; 11,38</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,46; 17,96</t>
+          <t>12,4; 17,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,46; 21,23</t>
+          <t>16,35; 21,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,87; 18,63</t>
+          <t>15,12; 18,96</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,11; 15,62</t>
+          <t>10,09; 15,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,66; 19,41</t>
+          <t>4,86; 19,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,64; 16,47</t>
+          <t>5,79; 16,34</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,24; 23,47</t>
+          <t>16,8; 23,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,73; 37,09</t>
+          <t>30,37; 36,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,77; 30,73</t>
+          <t>25,52; 30,6</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,44; 10,69</t>
+          <t>7,46; 10,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,05; 14,98</t>
+          <t>11,04; 14,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,85; 12,48</t>
+          <t>10,04; 12,56</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat)</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1857; 22469</t>
+          <t>1837; 23631</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14681; 39670</t>
+          <t>14089; 38635</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19215; 49336</t>
+          <t>18360; 49309</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13732; 38943</t>
+          <t>14262; 37429</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17610; 43248</t>
+          <t>18538; 44858</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37745; 72245</t>
+          <t>38633; 74501</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31062; 56001</t>
+          <t>31074; 55546</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33144; 52458</t>
+          <t>33146; 51683</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70751; 102309</t>
+          <t>70197; 102554</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28516; 97501</t>
+          <t>30518; 97372</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64559; 93770</t>
+          <t>65859; 94227</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87604; 178712</t>
+          <t>88574; 179848</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>68929; 99380</t>
+          <t>68596; 98529</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>88140; 113643</t>
+          <t>87511; 115009</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161909; 202783</t>
+          <t>164641; 206404</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36616; 56611</t>
+          <t>36545; 56697</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27928; 116356</t>
+          <t>29149; 116511</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63868; 158408</t>
+          <t>55664; 157190</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>44225; 63918</t>
+          <t>45760; 64990</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>125227; 151135</t>
+          <t>123775; 150670</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>175215; 208921</t>
+          <t>173506; 208004</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>254253; 365385</t>
+          <t>254826; 366914</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>397967; 539590</t>
+          <t>397866; 534397</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>691136; 875819</t>
+          <t>704388; 881414</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P57B_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,97</t>
+          <t>0,6; 5,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 12,34</t>
+          <t>5,01; 13,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,96</t>
+          <t>2,99; 7,52</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 8,87</t>
+          <t>3,73; 9,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 8,83</t>
+          <t>4,71; 9,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 8,01</t>
+          <t>4,82; 8,6</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>8,01%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,45</t>
+          <t>5,96; 10,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 9,6</t>
+          <t>6,32; 10,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 9,58</t>
+          <t>6,75; 9,57</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 11,07</t>
+          <t>7,98; 12,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,41; 13,46</t>
+          <t>10,24; 13,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,61; 11,38</t>
+          <t>9,86; 12,86</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,4; 17,81</t>
+          <t>12,47; 17,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,48</t>
+          <t>16,17; 21,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,12; 18,96</t>
+          <t>15,04; 18,68</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,09; 15,65</t>
+          <t>9,85; 15,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,86; 19,43</t>
+          <t>15,82; 21,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,79; 16,34</t>
+          <t>14,09; 17,75</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,8; 23,87</t>
+          <t>15,95; 23,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,37; 36,97</t>
+          <t>30,81; 37,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,52; 30,6</t>
+          <t>25,15; 30,5</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,46; 10,74</t>
+          <t>9,24; 11,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,04; 14,83</t>
+          <t>13,77; 15,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,04; 12,56</t>
+          <t>11,89; 13,27</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23625</t>
+          <t>29277</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31351</t>
+          <t>37487</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1837; 23631</t>
+          <t>2391; 22110</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14089; 38635</t>
+          <t>18074; 47533</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18360; 49309</t>
+          <t>22706; 57184</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>24340</t>
+          <t>29117</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30355</t>
+          <t>33985</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54694</t>
+          <t>63102</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14262; 37429</t>
+          <t>17715; 44463</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18538; 44858</t>
+          <t>23389; 46438</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38633; 74501</t>
+          <t>46894; 83597</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42576</t>
+          <t>49246</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42122</t>
+          <t>49612</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84697</t>
+          <t>98858</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31074; 55546</t>
+          <t>36706; 63848</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33146; 51683</t>
+          <t>39034; 62842</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70197; 102554</t>
+          <t>83322; 118042</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>64979</t>
+          <t>70003</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>79530</t>
+          <t>87457</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144509</t>
+          <t>157460</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30518; 97372</t>
+          <t>55227; 85861</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65859; 94227</t>
+          <t>74054; 100571</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88574; 179848</t>
+          <t>139534; 181996</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>83673</t>
+          <t>90826</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>100306</t>
+          <t>110434</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183978</t>
+          <t>201260</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>68596; 98529</t>
+          <t>74939; 107883</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>87511; 115009</t>
+          <t>96196; 126321</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164641; 206404</t>
+          <t>179754; 223355</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>46254</t>
+          <t>50214</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>73323</t>
+          <t>80170</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119577</t>
+          <t>130384</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36545; 56697</t>
+          <t>39484; 61845</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29149; 116511</t>
+          <t>68343; 91909</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55664; 157190</t>
+          <t>117295; 147779</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>54081</t>
+          <t>58295</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>138222</t>
+          <t>150597</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>192303</t>
+          <t>208892</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>45760; 64990</t>
+          <t>47657; 69758</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>123775; 150670</t>
+          <t>137185; 166457</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>173506; 208004</t>
+          <t>187193; 226947</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>323628</t>
+          <t>355911</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>487482</t>
+          <t>541532</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>811110</t>
+          <t>897443</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>254826; 366914</t>
+          <t>321937; 393887</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>397866; 534397</t>
+          <t>505520; 575781</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>704388; 881414</t>
+          <t>850906; 949298</t>
         </is>
       </c>
     </row>
